--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Mode2\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="165">
   <si>
     <t>怪物ID</t>
   </si>
@@ -123,6 +123,9 @@
     <t>近战前摇</t>
   </si>
   <si>
+    <t>远程前摇停顿帧</t>
+  </si>
+  <si>
     <t>远程弹速</t>
   </si>
   <si>
@@ -303,6 +306,9 @@
     <t>MeleeWindupSeconds</t>
   </si>
   <si>
+    <t>RangedWindupHoldFrame</t>
+  </si>
+  <si>
     <t>RangedProjectileSpeed</t>
   </si>
   <si>
@@ -363,226 +369,172 @@
     <t>25</t>
   </si>
   <si>
-    <t>1.0</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
-    <t>0.8</t>
-  </si>
-  <si>
     <t>0.25</t>
   </si>
   <si>
+    <t>MSkill_SelfRevive_1;0</t>
+  </si>
+  <si>
+    <t>Attack1|Attack2|Attack3|Attack4</t>
+  </si>
+  <si>
+    <t>Walk</t>
+  </si>
+  <si>
+    <t>Run</t>
+  </si>
+  <si>
+    <t>HPPK_UI_Monster_01</t>
+  </si>
+  <si>
+    <t>Monster_02</t>
+  </si>
+  <si>
+    <t>MonsterModel_03;10</t>
+  </si>
+  <si>
+    <t>胖子僵尸</t>
+  </si>
+  <si>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>HPPK_UI_Monster_02</t>
+  </si>
+  <si>
+    <t>Monster_03</t>
+  </si>
+  <si>
+    <t>MonsterModel_05;10</t>
+  </si>
+  <si>
+    <t>墓园犬</t>
+  </si>
+  <si>
+    <t>PreferProtagonist</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>HPPK_UI_Monster_03</t>
+  </si>
+  <si>
+    <t>Monster_04</t>
+  </si>
+  <si>
+    <t>HPPK_UI_Monster_04</t>
+  </si>
+  <si>
+    <t>Monster_05</t>
+  </si>
+  <si>
+    <t>石像鬼</t>
+  </si>
+  <si>
+    <t>PreferWarrior</t>
+  </si>
+  <si>
+    <t>145</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Monster_06</t>
+  </si>
+  <si>
+    <t>巫妖徒</t>
+  </si>
+  <si>
+    <t>175</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Monster_07</t>
+  </si>
+  <si>
+    <t>骨龙幼崽</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Monster_08</t>
+  </si>
+  <si>
+    <t>血仆</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>Monster_09</t>
+  </si>
+  <si>
+    <t>暗影刺客</t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>Monster_10</t>
+  </si>
+  <si>
+    <t>巨型僵尸</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>Monster_11</t>
+  </si>
+  <si>
+    <t>MonsterModel_06;10</t>
+  </si>
+  <si>
+    <t>骷髅猛士</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>0.3</t>
   </si>
   <si>
-    <t>MSkill_SelfRevive_1;0</t>
-  </si>
-  <si>
-    <t>Attack1|Attack2|Attack3|Attack4</t>
-  </si>
-  <si>
-    <t>Walk</t>
-  </si>
-  <si>
-    <t>Run</t>
-  </si>
-  <si>
-    <t>HPPK_UI_Monster_01</t>
-  </si>
-  <si>
-    <t>Monster_02</t>
-  </si>
-  <si>
-    <t>MonsterModel_03;10</t>
-  </si>
-  <si>
-    <t>胖子僵尸</t>
-  </si>
-  <si>
-    <t>Ranged</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>0.85</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>HPPK_UI_Monster_02</t>
-  </si>
-  <si>
-    <t>Monster_03</t>
-  </si>
-  <si>
-    <t>MonsterModel_05;10</t>
-  </si>
-  <si>
-    <t>墓园犬</t>
-  </si>
-  <si>
-    <t>PreferProtagonist</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>0.9</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>HPPK_UI_Monster_03</t>
-  </si>
-  <si>
-    <t>Monster_04</t>
-  </si>
-  <si>
-    <t>HPPK_UI_Monster_04</t>
-  </si>
-  <si>
-    <t>Monster_05</t>
-  </si>
-  <si>
-    <t>石像鬼</t>
-  </si>
-  <si>
-    <t>PreferWarrior</t>
-  </si>
-  <si>
-    <t>145</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Monster_06</t>
-  </si>
-  <si>
-    <t>巫妖徒</t>
-  </si>
-  <si>
-    <t>175</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>1.05</t>
-  </si>
-  <si>
-    <t>0.4</t>
-  </si>
-  <si>
-    <t>Monster_07</t>
-  </si>
-  <si>
-    <t>骨龙幼崽</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>1.1</t>
   </si>
   <si>
-    <t>0.42</t>
-  </si>
-  <si>
-    <t>Monster_08</t>
-  </si>
-  <si>
-    <t>血仆</t>
-  </si>
-  <si>
-    <t>235</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>1.15</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>Monster_09</t>
-  </si>
-  <si>
-    <t>暗影刺客</t>
-  </si>
-  <si>
-    <t>265</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>0.46</t>
-  </si>
-  <si>
-    <t>Monster_10</t>
-  </si>
-  <si>
-    <t>巨型僵尸</t>
-  </si>
-  <si>
-    <t>295</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>0.48</t>
-  </si>
-  <si>
-    <t>Monster_11</t>
-  </si>
-  <si>
-    <t>MonsterModel_06;10</t>
-  </si>
-  <si>
-    <t>骷髅猛士</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>2000</t>
-  </si>
-  <si>
-    <t>0.6</t>
   </si>
   <si>
     <t>1500</t>
@@ -1090,148 +1042,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1589,19 +1541,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AE15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="11.725" customWidth="1"/>
-    <col min="2" max="2" width="22.25" customWidth="1"/>
-    <col min="4" max="4" width="15.25" customWidth="1"/>
+    <col min="1" max="1" width="11.7272727272727" customWidth="1"/>
+    <col min="2" max="2" width="22.2727272727273" customWidth="1"/>
+    <col min="4" max="4" width="15.2727272727273" customWidth="1"/>
     <col min="6" max="6" width="13" style="2" customWidth="1"/>
-    <col min="7" max="7" width="12.25" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
-    <col min="26" max="26" width="17.25" customWidth="1"/>
+    <col min="7" max="7" width="12.2727272727273" customWidth="1"/>
+    <col min="25" max="25" width="8.36363636363636" customWidth="1"/>
+    <col min="27" max="27" width="17.2727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1692,75 +1644,75 @@
       <c r="AD1" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="S2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="T2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V2" t="s">
-        <v>51</v>
-      </c>
-      <c r="W2" t="s">
         <v>52</v>
       </c>
       <c r="X2" t="s">
@@ -1784,1135 +1736,1177 @@
       <c r="AD2" t="s">
         <v>59</v>
       </c>
+      <c r="AE2" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:30">
+    <row r="3" s="1" customFormat="1" spans="1:31">
       <c r="A3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AD3" t="s">
         <v>89</v>
       </c>
+      <c r="AD3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>91</v>
+      </c>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:31">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N4" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O4" s="2">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="Q4" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="T4" s="2" t="s">
         <v>104</v>
+      </c>
+      <c r="T4" s="2">
+        <v>0.5</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="V4" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W4" s="2">
+        <v>0</v>
+      </c>
+      <c r="X4" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z4" t="s">
         <v>106</v>
       </c>
-      <c r="W4" t="s">
+      <c r="AA4" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
+      <c r="A5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="X4" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30">
-      <c r="A5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="J5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G5" t="s">
-        <v>96</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>118</v>
+      <c r="T5" s="2">
+        <v>0.5</v>
       </c>
       <c r="U5" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="V5" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W5" s="2">
+        <v>3</v>
+      </c>
+      <c r="X5">
+        <v>5</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
+      <c r="A6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="W5" t="s">
-        <v>119</v>
-      </c>
-      <c r="X5" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30">
-      <c r="A6" t="s">
+      <c r="J6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B6" t="s">
+      <c r="N6" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O6" s="2">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G6" t="s">
-        <v>96</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>128</v>
+      <c r="T6" s="2">
+        <v>0.5</v>
       </c>
       <c r="U6" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="W6" t="s">
-        <v>100</v>
+      <c r="V6" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W6" s="2">
+        <v>0</v>
       </c>
       <c r="X6" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z6" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB6" t="s">
         <v>108</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AC6" t="s">
         <v>109</v>
       </c>
-      <c r="AB6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>130</v>
+      <c r="AE6" t="s">
+        <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:31">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H7" s="2">
         <v>10</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>102</v>
+      <c r="O7" s="2">
+        <v>1.5</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="T7" s="2" t="s">
         <v>104</v>
+      </c>
+      <c r="T7" s="2">
+        <v>0.5</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="V7" s="2" t="s">
+      <c r="V7" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W7" s="2">
+        <v>0</v>
+      </c>
+      <c r="X7" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z7" t="s">
         <v>106</v>
       </c>
-      <c r="W7" t="s">
+      <c r="AA7" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31">
+      <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" t="s">
+        <v>98</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="X7" t="s">
-        <v>100</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA7" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30">
-      <c r="A8" t="s">
-        <v>133</v>
-      </c>
-      <c r="B8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G8" t="s">
-        <v>96</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>102</v>
+        <v>130</v>
+      </c>
+      <c r="N8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O8" s="2">
+        <v>1</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>95</v>
+        <v>131</v>
+      </c>
+      <c r="T8" s="2">
+        <v>0.5</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="V8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W8" s="2">
+        <v>3</v>
+      </c>
+      <c r="X8">
+        <v>5</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31">
+      <c r="A9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="W8" t="s">
-        <v>138</v>
-      </c>
-      <c r="X8" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30">
-      <c r="A9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" t="s">
-        <v>96</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
+      </c>
+      <c r="O9" s="2">
+        <v>1.5</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
+      </c>
+      <c r="T9" s="2">
+        <v>0.5</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="V9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="W9" t="s">
+      <c r="V9" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W9" s="2">
+        <v>0</v>
+      </c>
+      <c r="X9" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31">
+      <c r="A10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="X9" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30">
-      <c r="A10" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D10" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" t="s">
-        <v>96</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>102</v>
+        <v>138</v>
+      </c>
+      <c r="N10" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O10" s="2">
+        <v>1</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
+      </c>
+      <c r="T10" s="2">
+        <v>0.5</v>
       </c>
       <c r="U10" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="V10" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="W10" t="s">
+      <c r="V10" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W10" s="2">
+        <v>0</v>
+      </c>
+      <c r="X10" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
+      <c r="A11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="X10" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30">
-      <c r="A11" t="s">
-        <v>151</v>
-      </c>
-      <c r="B11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="D11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E11" t="s">
-        <v>115</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G11" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
+      </c>
+      <c r="O11" s="2">
+        <v>1.5</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>155</v>
+        <v>143</v>
+      </c>
+      <c r="T11" s="2">
+        <v>0.5</v>
       </c>
       <c r="U11" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="V11" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W11" s="2">
+        <v>3</v>
+      </c>
+      <c r="X11">
+        <v>5</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
+      <c r="A12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="W11" t="s">
-        <v>156</v>
-      </c>
-      <c r="X11" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30">
-      <c r="A12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D12" t="s">
-        <v>125</v>
-      </c>
-      <c r="E12" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G12" t="s">
-        <v>96</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>102</v>
+        <v>146</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="O12" s="2">
+        <v>1</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>161</v>
+        <v>147</v>
+      </c>
+      <c r="T12" s="2">
+        <v>0.5</v>
       </c>
       <c r="U12" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="V12" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W12" s="2">
+        <v>0</v>
+      </c>
+      <c r="X12" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
+      <c r="A13" t="s">
+        <v>148</v>
+      </c>
+      <c r="B13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O13" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="T13" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="V13" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W13" s="2">
+        <v>0</v>
+      </c>
+      <c r="X13" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31">
+      <c r="A14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C14" t="s">
+        <v>155</v>
+      </c>
+      <c r="D14" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G14" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="O14" s="2">
+        <v>1</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="T14" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="V14" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W14" s="2">
+        <v>0</v>
+      </c>
+      <c r="X14" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>109</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31">
+      <c r="A15" t="s">
         <v>162</v>
       </c>
-      <c r="W12" t="s">
-        <v>100</v>
-      </c>
-      <c r="X12" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z12" t="s">
+      <c r="B15" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="N15" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="O15" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="W15" s="2">
+        <v>0</v>
+      </c>
+      <c r="X15" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB15" t="s">
         <v>108</v>
       </c>
-      <c r="AA12" t="s">
+      <c r="AC15" t="s">
         <v>109</v>
       </c>
-      <c r="AB12" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30">
-      <c r="A13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" t="s">
-        <v>96</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="W13" t="s">
-        <v>100</v>
-      </c>
-      <c r="X13" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30">
-      <c r="A14" t="s">
-        <v>170</v>
-      </c>
-      <c r="B14" t="s">
-        <v>171</v>
-      </c>
-      <c r="C14" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" t="s">
-        <v>96</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="W14" t="s">
-        <v>100</v>
-      </c>
-      <c r="X14" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30">
-      <c r="A15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" t="s">
-        <v>96</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="W15" t="s">
-        <v>100</v>
-      </c>
-      <c r="X15" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>109</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>132</v>
+      <c r="AE15" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Mode2/Excel/防守_怪物配置表_Defend_MonsterConfig.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="165">
   <si>
     <t>怪物ID</t>
   </si>
@@ -1876,13 +1876,13 @@
         <v>103</v>
       </c>
       <c r="N4" s="2">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="O4" s="2">
         <v>1</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>101</v>
+      <c r="P4" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q4" s="2" t="s">
         <v>97</v>
@@ -1967,14 +1967,14 @@
       <c r="M5" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>101</v>
+      <c r="N5" s="2">
+        <v>0.8</v>
       </c>
       <c r="O5" s="2">
         <v>1.5</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>101</v>
+      <c r="P5" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q5" s="2" t="s">
         <v>97</v>
@@ -2057,13 +2057,13 @@
         <v>122</v>
       </c>
       <c r="N6" s="2">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="O6" s="2">
         <v>1</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>101</v>
+      <c r="P6" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>97</v>
@@ -2145,14 +2145,14 @@
       <c r="M7" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>101</v>
+      <c r="N7" s="2">
+        <v>0.8</v>
       </c>
       <c r="O7" s="2">
         <v>1.5</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>101</v>
+      <c r="P7" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>97</v>
@@ -2238,13 +2238,13 @@
         <v>130</v>
       </c>
       <c r="N8" s="2">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="O8" s="2">
         <v>1</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>101</v>
+      <c r="P8" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>97</v>
@@ -2326,14 +2326,14 @@
       <c r="M9" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>101</v>
+      <c r="N9" s="2">
+        <v>0.8</v>
       </c>
       <c r="O9" s="2">
         <v>1.5</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>101</v>
+      <c r="P9" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q9" s="2" t="s">
         <v>97</v>
@@ -2416,13 +2416,13 @@
         <v>138</v>
       </c>
       <c r="N10" s="2">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="O10" s="2">
         <v>1</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>101</v>
+      <c r="P10" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>97</v>
@@ -2504,14 +2504,14 @@
       <c r="M11" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="N11" s="2" t="s">
-        <v>101</v>
+      <c r="N11" s="2">
+        <v>0.8</v>
       </c>
       <c r="O11" s="2">
         <v>1.5</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>101</v>
+      <c r="P11" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>97</v>
@@ -2594,13 +2594,13 @@
         <v>146</v>
       </c>
       <c r="N12" s="2">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="O12" s="2">
         <v>1</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>101</v>
+      <c r="P12" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>97</v>
@@ -2682,14 +2682,14 @@
       <c r="M13" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="N13" s="2" t="s">
-        <v>101</v>
+      <c r="N13" s="2">
+        <v>0.8</v>
       </c>
       <c r="O13" s="2">
         <v>1.5</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>101</v>
+      <c r="P13" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q13" s="2" t="s">
         <v>97</v>
@@ -2771,14 +2771,14 @@
       <c r="M14" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="N14" s="2" t="s">
-        <v>157</v>
+      <c r="N14" s="2">
+        <v>0.5</v>
       </c>
       <c r="O14" s="2">
         <v>1</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>101</v>
+      <c r="P14" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>97</v>
@@ -2861,13 +2861,13 @@
         <v>163</v>
       </c>
       <c r="N15" s="2">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O15" s="2">
         <v>1.5</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>101</v>
+      <c r="P15" s="2">
+        <v>0.3</v>
       </c>
       <c r="Q15" s="2" t="s">
         <v>97</v>
